--- a/output/semanal/01_perfil_semanal.xlsx
+++ b/output/semanal/01_perfil_semanal.xlsx
@@ -22,13 +22,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -423,12 +435,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>metrica</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -475,7 +487,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6">
@@ -499,31 +511,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>nulos</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ceros_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>valores_unicos</t>
         </is>
@@ -670,10 +682,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.4550561797752809</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -712,10 +724,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2078651685393259</v>
+        <v>0.4044943820224719</v>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -754,10 +766,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1853932584269663</v>
+        <v>0.3595505617977528</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -1135,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31">
@@ -1366,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42">
@@ -1456,117 +1468,117 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>exog_eventos_festivos_semana</t>
+          <t>hist_ventas_total_items_lag_1s</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8595505617977528</v>
+        <v>0.1741573033707865</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>exog_eventos_pago_semana</t>
+          <t>hist_ventas_total_items_lag_2s</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5393258426966292</v>
+        <v>0.1685393258426966</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>exog_es_san_valentin</t>
+          <t>hist_ventas_total_items_lag_4s</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9775280898876404</v>
+        <v>0.1685393258426966</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>exog_es_dia_nino</t>
+          <t>hist_ventas_total_items_lag_8s</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9775280898876404</v>
+        <v>0.1685393258426966</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>exog_es_dia_madre</t>
+          <t>hist_ventas_total_items_lag_52s</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9775280898876404</v>
+        <v>0.3146067415730337</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>exog_semana_anio_sin</t>
+          <t>hist_ventas_total_items_media_4s</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1576,18 +1588,18 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>44</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>exog_semana_anio_cos</t>
+          <t>hist_ventas_total_items_desv_4s</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1597,18 +1609,18 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>47</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>exog_mes_sin</t>
+          <t>hist_ventas_total_items_media_8s</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1618,18 +1630,18 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>11</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>exog_mes_cos</t>
+          <t>hist_ventas_total_items_desv_8s</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1639,18 +1651,18 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>exog_nacimientos_indice_publicado_lag_1s</t>
+          <t>hist_ventas_total_items_media_12s</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1660,18 +1672,18 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>exog_inpc_publicado_lag_1s</t>
+          <t>hist_ventas_total_items_desv_12s</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>exógena</t>
+          <t>histórica</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1681,27 +1693,1182 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>36</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>hist_ventas_pastel_lag_1s</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.4775280898876405</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>hist_ventas_pastel_lag_2s</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.4775280898876405</v>
+      </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>hist_ventas_pastel_lag_4s</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.4775280898876405</v>
+      </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>hist_ventas_pastel_lag_8s</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.4775280898876405</v>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>hist_ventas_pastel_lag_52s</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.5617977528089888</v>
+      </c>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>hist_ventas_pastel_media_4s</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.03932584269662921</v>
+      </c>
+      <c r="E62" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>hist_ventas_pastel_desv_4s</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.0449438202247191</v>
+      </c>
+      <c r="E63" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>hist_ventas_pastel_media_8s</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>hist_ventas_pastel_desv_8s</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>hist_ventas_pastel_media_12s</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>hist_ventas_pastel_desv_12s</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_lag_1s</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.7471910112359551</v>
+      </c>
+      <c r="E68" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_lag_2s</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.7471910112359551</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_lag_4s</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.7415730337078652</v>
+      </c>
+      <c r="E70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_lag_8s</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.7359550561797753</v>
+      </c>
+      <c r="E71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_lag_52s</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.7640449438202247</v>
+      </c>
+      <c r="E72" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_media_4s</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.449438202247191</v>
+      </c>
+      <c r="E73" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_desv_4s</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.449438202247191</v>
+      </c>
+      <c r="E74" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_media_8s</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.2752808988764045</v>
+      </c>
+      <c r="E75" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_desv_8s</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.2752808988764045</v>
+      </c>
+      <c r="E76" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_media_12s</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.151685393258427</v>
+      </c>
+      <c r="E77" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>hist_ventas_galletas_desv_12s</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.151685393258427</v>
+      </c>
+      <c r="E78" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_lag_1s</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.9719101123595506</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_lag_2s</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.9719101123595506</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_lag_4s</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.9719101123595506</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_lag_8s</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.9719101123595506</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_lag_52s</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.9775280898876404</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_media_4s</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.8876404494382022</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_desv_4s</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.8876404494382022</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_media_8s</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.7752808988764045</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_desv_8s</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.7752808988764045</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_media_12s</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.6741573033707865</v>
+      </c>
+      <c r="E88" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>hist_ventas_otros_desv_12s</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.6741573033707865</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_lag_1s</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.5056179775280899</v>
+      </c>
+      <c r="E90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_lag_2s</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E91" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_lag_4s</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.4887640449438202</v>
+      </c>
+      <c r="E92" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_lag_8s</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.4943820224719101</v>
+      </c>
+      <c r="E93" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_lag_52s</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.5561797752808989</v>
+      </c>
+      <c r="E94" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_media_4s</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="E95" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_desv_4s</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.1348314606741573</v>
+      </c>
+      <c r="E96" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_media_8s</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01685393258426966</v>
+      </c>
+      <c r="E97" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_desv_8s</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01685393258426966</v>
+      </c>
+      <c r="E98" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_media_12s</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>hist_ventas_cupcakes_desv_12s</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>histórica</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>exog_eventos_festivos_semana</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.8595505617977528</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>exog_eventos_pago_semana</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.5393258426966292</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>exog_es_san_valentin</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.9775280898876404</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>exog_es_dia_nino</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.9775280898876404</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>exog_es_dia_madre</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.9775280898876404</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>exog_semana_anio_sin</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>exog_semana_anio_cos</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>exog_mes_sin</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>exog_mes_cos</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>exog_nacimientos_indice_publicado_lag_1s</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>exog_inpc_publicado_lag_1s</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>exógena</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>exog_temperatura_publicado_lag_1s</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>exógena</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
         <v>67</v>
       </c>
     </row>
@@ -1720,19 +2887,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>semana_inicio</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>target_compras_importe_semanal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44928</v>
       </c>
       <c r="B2" t="n">
@@ -1740,7 +2907,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44935</v>
       </c>
       <c r="B3" t="n">
@@ -1748,7 +2915,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44942</v>
       </c>
       <c r="B4" t="n">
@@ -1756,7 +2923,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44949</v>
       </c>
       <c r="B5" t="n">
@@ -1764,7 +2931,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44956</v>
       </c>
       <c r="B6" t="n">
@@ -1772,7 +2939,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44963</v>
       </c>
       <c r="B7" t="n">
@@ -1780,7 +2947,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="B8" t="n">
@@ -1788,7 +2955,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44977</v>
       </c>
       <c r="B9" t="n">
@@ -1796,7 +2963,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="B10" t="n">
@@ -1804,7 +2971,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44991</v>
       </c>
       <c r="B11" t="n">
@@ -1812,7 +2979,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44998</v>
       </c>
       <c r="B12" t="n">
@@ -1820,7 +2987,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45005</v>
       </c>
       <c r="B13" t="n">
@@ -1828,7 +2995,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45012</v>
       </c>
       <c r="B14" t="n">
@@ -1836,7 +3003,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45019</v>
       </c>
       <c r="B15" t="n">
@@ -1844,7 +3011,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45026</v>
       </c>
       <c r="B16" t="n">
@@ -1852,7 +3019,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45033</v>
       </c>
       <c r="B17" t="n">
@@ -1860,7 +3027,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="B18" t="n">
@@ -1868,7 +3035,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B19" t="n">
@@ -1876,7 +3043,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +3051,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45061</v>
       </c>
       <c r="B21" t="n">
@@ -1892,7 +3059,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45068</v>
       </c>
       <c r="B22" t="n">
@@ -1900,7 +3067,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45075</v>
       </c>
       <c r="B23" t="n">
@@ -1908,7 +3075,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45082</v>
       </c>
       <c r="B24" t="n">
@@ -1916,7 +3083,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45089</v>
       </c>
       <c r="B25" t="n">
@@ -1924,7 +3091,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45096</v>
       </c>
       <c r="B26" t="n">
@@ -1932,7 +3099,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="B27" t="n">
@@ -1940,7 +3107,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45110</v>
       </c>
       <c r="B28" t="n">
@@ -1948,7 +3115,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45117</v>
       </c>
       <c r="B29" t="n">
@@ -1956,7 +3123,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45124</v>
       </c>
       <c r="B30" t="n">
@@ -1964,7 +3131,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="B31" t="n">
@@ -1972,7 +3139,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B32" t="n">
@@ -1980,7 +3147,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="B33" t="n">
@@ -1988,7 +3155,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45152</v>
       </c>
       <c r="B34" t="n">
@@ -1996,7 +3163,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45159</v>
       </c>
       <c r="B35" t="n">
@@ -2004,7 +3171,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45166</v>
       </c>
       <c r="B36" t="n">
@@ -2012,7 +3179,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45173</v>
       </c>
       <c r="B37" t="n">
@@ -2020,7 +3187,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45180</v>
       </c>
       <c r="B38" t="n">
@@ -2028,7 +3195,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45187</v>
       </c>
       <c r="B39" t="n">
@@ -2036,7 +3203,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45194</v>
       </c>
       <c r="B40" t="n">
@@ -2044,7 +3211,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45201</v>
       </c>
       <c r="B41" t="n">
@@ -2052,7 +3219,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45208</v>
       </c>
       <c r="B42" t="n">
@@ -2060,7 +3227,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45215</v>
       </c>
       <c r="B43" t="n">
@@ -2068,7 +3235,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="B44" t="n">
@@ -2076,7 +3243,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45229</v>
       </c>
       <c r="B45" t="n">
@@ -2084,7 +3251,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45236</v>
       </c>
       <c r="B46" t="n">
@@ -2092,7 +3259,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45243</v>
       </c>
       <c r="B47" t="n">
@@ -2100,7 +3267,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45250</v>
       </c>
       <c r="B48" t="n">
@@ -2108,7 +3275,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45257</v>
       </c>
       <c r="B49" t="n">
@@ -2116,7 +3283,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45264</v>
       </c>
       <c r="B50" t="n">
@@ -2124,7 +3291,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45271</v>
       </c>
       <c r="B51" t="n">
@@ -2132,7 +3299,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45278</v>
       </c>
       <c r="B52" t="n">
@@ -2140,7 +3307,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45285</v>
       </c>
       <c r="B53" t="n">
@@ -2148,7 +3315,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B54" t="n">
@@ -2156,7 +3323,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45299</v>
       </c>
       <c r="B55" t="n">
@@ -2164,7 +3331,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45306</v>
       </c>
       <c r="B56" t="n">
@@ -2172,7 +3339,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45313</v>
       </c>
       <c r="B57" t="n">
@@ -2180,7 +3347,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="B58" t="n">
@@ -2188,7 +3355,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="B59" t="n">
@@ -2196,7 +3363,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="B60" t="n">
@@ -2204,7 +3371,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45341</v>
       </c>
       <c r="B61" t="n">
@@ -2212,7 +3379,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="B62" t="n">
@@ -2220,7 +3387,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45355</v>
       </c>
       <c r="B63" t="n">
@@ -2228,7 +3395,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45362</v>
       </c>
       <c r="B64" t="n">
@@ -2236,7 +3403,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45369</v>
       </c>
       <c r="B65" t="n">
@@ -2244,7 +3411,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="B66" t="n">
@@ -2252,7 +3419,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B67" t="n">
@@ -2260,7 +3427,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45390</v>
       </c>
       <c r="B68" t="n">
@@ -2268,7 +3435,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45397</v>
       </c>
       <c r="B69" t="n">
@@ -2276,7 +3443,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45404</v>
       </c>
       <c r="B70" t="n">
@@ -2284,7 +3451,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="B71" t="n">
@@ -2292,7 +3459,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="B72" t="n">
@@ -2300,7 +3467,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45425</v>
       </c>
       <c r="B73" t="n">
@@ -2308,7 +3475,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45432</v>
       </c>
       <c r="B74" t="n">
@@ -2316,7 +3483,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45439</v>
       </c>
       <c r="B75" t="n">
@@ -2324,7 +3491,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45446</v>
       </c>
       <c r="B76" t="n">
@@ -2332,7 +3499,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45453</v>
       </c>
       <c r="B77" t="n">
@@ -2340,7 +3507,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B78" t="n">
@@ -2348,7 +3515,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B79" t="n">
@@ -2356,7 +3523,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B80" t="n">
@@ -2364,7 +3531,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B81" t="n">
@@ -2372,7 +3539,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="B82" t="n">
@@ -2380,7 +3547,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45495</v>
       </c>
       <c r="B83" t="n">
@@ -2388,7 +3555,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="B84" t="n">
@@ -2396,7 +3563,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="B85" t="n">
@@ -2404,7 +3571,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45516</v>
       </c>
       <c r="B86" t="n">
@@ -2412,7 +3579,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45523</v>
       </c>
       <c r="B87" t="n">
@@ -2420,7 +3587,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45530</v>
       </c>
       <c r="B88" t="n">
@@ -2428,7 +3595,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45537</v>
       </c>
       <c r="B89" t="n">
@@ -2436,7 +3603,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B90" t="n">
@@ -2444,7 +3611,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B91" t="n">
@@ -2452,7 +3619,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B92" t="n">
@@ -2460,7 +3627,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B93" t="n">
@@ -2468,7 +3635,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="B94" t="n">
@@ -2476,7 +3643,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45579</v>
       </c>
       <c r="B95" t="n">
@@ -2484,7 +3651,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B96" t="n">
@@ -2492,7 +3659,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45593</v>
       </c>
       <c r="B97" t="n">
@@ -2500,7 +3667,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="B98" t="n">
@@ -2508,7 +3675,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45607</v>
       </c>
       <c r="B99" t="n">
@@ -2516,7 +3683,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45614</v>
       </c>
       <c r="B100" t="n">
@@ -2524,7 +3691,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45621</v>
       </c>
       <c r="B101" t="n">
@@ -2532,7 +3699,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45628</v>
       </c>
       <c r="B102" t="n">
@@ -2540,7 +3707,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45635</v>
       </c>
       <c r="B103" t="n">
@@ -2548,7 +3715,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45642</v>
       </c>
       <c r="B104" t="n">
@@ -2556,7 +3723,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45649</v>
       </c>
       <c r="B105" t="n">
@@ -2564,7 +3731,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45656</v>
       </c>
       <c r="B106" t="n">
@@ -2572,7 +3739,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45663</v>
       </c>
       <c r="B107" t="n">
@@ -2580,7 +3747,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="B108" t="n">
@@ -2588,7 +3755,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45677</v>
       </c>
       <c r="B109" t="n">
@@ -2596,7 +3763,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="B110" t="n">
@@ -2604,7 +3771,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="B111" t="n">
@@ -2612,7 +3779,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="B112" t="n">
@@ -2620,7 +3787,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45705</v>
       </c>
       <c r="B113" t="n">
@@ -2628,7 +3795,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="B114" t="n">
@@ -2636,7 +3803,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45719</v>
       </c>
       <c r="B115" t="n">
@@ -2644,7 +3811,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="B116" t="n">
@@ -2652,7 +3819,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45733</v>
       </c>
       <c r="B117" t="n">
@@ -2660,7 +3827,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="B118" t="n">
@@ -2668,7 +3835,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B119" t="n">
@@ -2676,7 +3843,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45754</v>
       </c>
       <c r="B120" t="n">
@@ -2684,7 +3851,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="B121" t="n">
@@ -2692,7 +3859,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45768</v>
       </c>
       <c r="B122" t="n">
@@ -2700,7 +3867,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="B123" t="n">
@@ -2708,7 +3875,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="B124" t="n">
@@ -2716,7 +3883,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="B125" t="n">
@@ -2724,7 +3891,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45796</v>
       </c>
       <c r="B126" t="n">
@@ -2732,7 +3899,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="B127" t="n">
@@ -2740,7 +3907,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45810</v>
       </c>
       <c r="B128" t="n">
@@ -2748,7 +3915,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="B129" t="n">
@@ -2756,7 +3923,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B130" t="n">
@@ -2764,7 +3931,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B131" t="n">
@@ -2772,7 +3939,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B132" t="n">
@@ -2780,7 +3947,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45845</v>
       </c>
       <c r="B133" t="n">
@@ -2788,7 +3955,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B134" t="n">
@@ -2796,7 +3963,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="B135" t="n">
@@ -2804,7 +3971,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="B136" t="n">
@@ -2812,7 +3979,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="B137" t="n">
@@ -2820,7 +3987,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="B138" t="n">
@@ -2828,7 +3995,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45887</v>
       </c>
       <c r="B139" t="n">
@@ -2836,7 +4003,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="B140" t="n">
@@ -2844,7 +4011,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B141" t="n">
@@ -2852,7 +4019,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="B142" t="n">
@@ -2860,7 +4027,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45915</v>
       </c>
       <c r="B143" t="n">
@@ -2868,7 +4035,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="B144" t="n">
@@ -2876,7 +4043,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45929</v>
       </c>
       <c r="B145" t="n">
@@ -2884,7 +4051,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45936</v>
       </c>
       <c r="B146" t="n">
@@ -2892,7 +4059,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="B147" t="n">
@@ -2900,7 +4067,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45950</v>
       </c>
       <c r="B148" t="n">
@@ -2908,7 +4075,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="B149" t="n">
@@ -2916,7 +4083,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="B150" t="n">
@@ -2924,7 +4091,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="B151" t="n">
@@ -2932,7 +4099,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45978</v>
       </c>
       <c r="B152" t="n">
@@ -2940,7 +4107,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="B153" t="n">
@@ -2948,7 +4115,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B154" t="n">
@@ -2956,7 +4123,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="B155" t="n">
@@ -2964,7 +4131,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>46006</v>
       </c>
       <c r="B156" t="n">
@@ -2972,7 +4139,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="B157" t="n">
@@ -2980,7 +4147,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B158" t="n">
@@ -2988,7 +4155,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>46027</v>
       </c>
       <c r="B159" t="n">
@@ -2996,7 +4163,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>46034</v>
       </c>
       <c r="B160" t="n">
@@ -3004,7 +4171,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>46041</v>
       </c>
       <c r="B161" t="n">
@@ -3012,7 +4179,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>46048</v>
       </c>
       <c r="B162" t="n">
@@ -3020,7 +4187,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46055</v>
       </c>
       <c r="B163" t="n">
@@ -3028,7 +4195,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="B164" t="n">
@@ -3036,7 +4203,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46069</v>
       </c>
       <c r="B165" t="n">
@@ -3044,7 +4211,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="B166" t="n">
@@ -3052,7 +4219,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="B167" t="n">
@@ -3060,7 +4227,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46090</v>
       </c>
       <c r="B168" t="n">
@@ -3068,7 +4235,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B169" t="n">
@@ -3076,7 +4243,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46104</v>
       </c>
       <c r="B170" t="n">
@@ -3084,7 +4251,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="B171" t="n">
@@ -3092,7 +4259,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="B172" t="n">
@@ -3100,7 +4267,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="B173" t="n">
@@ -3108,7 +4275,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="B174" t="n">
@@ -3116,7 +4283,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="B175" t="n">
@@ -3124,7 +4291,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="B176" t="n">
@@ -3132,7 +4299,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="B177" t="n">
@@ -3140,7 +4307,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B178" t="n">
@@ -3148,7 +4315,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="B179" t="n">
